--- a/data/trans_camb/POLIPATOLOGIA_Lim_5-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_5-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 3,15</t>
+          <t>-3,41; 3,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 0,94</t>
+          <t>-4,15; 1,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 10,1</t>
+          <t>-0,09; 11,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 1,05</t>
+          <t>-7,19; 1,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,83</t>
+          <t>-1,09; 5,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 0,05</t>
+          <t>-4,67; 0,27</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-61,11; 143,96</t>
+          <t>-63,86; 152,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-76,83; 48,01</t>
+          <t>-73,8; 54,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 177,66</t>
+          <t>-3,41; 182,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,93; 21,38</t>
+          <t>-61,11; 20,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 121,03</t>
+          <t>-14,58; 116,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,37; 2,16</t>
+          <t>-58,64; 6,19</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,59; -2,09</t>
+          <t>-7,0; -2,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 2,91</t>
+          <t>-3,35; 2,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,9; -0,26</t>
+          <t>-6,95; -0,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 7,5</t>
+          <t>0,82; 7,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,72; -1,49</t>
+          <t>-5,94; -1,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 4,39</t>
+          <t>-0,43; 4,3</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-94,02; -48,54</t>
+          <t>-93,77; -50,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,66; 77,99</t>
+          <t>-48,37; 87,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,56; -0,43</t>
+          <t>-63,73; -0,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 109,87</t>
+          <t>5,11; 111,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,36; -24,83</t>
+          <t>-70,05; -29,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 77,26</t>
+          <t>-5,37; 73,4</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,7</t>
+          <t>-3,83; 0,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,68; 12,08</t>
+          <t>4,55; 11,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 1,23</t>
+          <t>-7,16; 1,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,24; 12,26</t>
+          <t>3,38; 12,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,31</t>
+          <t>-4,67; 0,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 10,7</t>
+          <t>5,01; 10,85</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-86,25; 61,02</t>
+          <t>-85,64; 82,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>81,99; 804,29</t>
+          <t>73,57; 853,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-67,09; 22,86</t>
+          <t>-65,85; 28,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28,9; 217,18</t>
+          <t>26,75; 220,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,24; 9,62</t>
+          <t>-65,32; 4,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65,28; 267,37</t>
+          <t>68,57; 255,73</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 3,76</t>
+          <t>-2,4; 3,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 9,58</t>
+          <t>1,86; 9,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 4,13</t>
+          <t>-5,4; 4,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 3,84</t>
+          <t>-7,51; 3,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 2,84</t>
+          <t>-3,1; 2,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 5,44</t>
+          <t>-1,67; 5,34</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-44,2; 150,39</t>
+          <t>-45,86; 140,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27,44; 345,48</t>
+          <t>28,32; 362,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,7; 36,76</t>
+          <t>-34,96; 39,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,09; 31,58</t>
+          <t>-47,0; 31,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,73; 37,1</t>
+          <t>-31,24; 34,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 71,77</t>
+          <t>-15,73; 70,1</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 0,95</t>
+          <t>-8,44; 1,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 1,82</t>
+          <t>-7,41; 1,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,86; -0,94</t>
+          <t>-13,98; -0,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 0,3</t>
+          <t>-15,33; -0,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,33; -1,7</t>
+          <t>-10,15; -1,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,48; -0,1</t>
+          <t>-8,73; 0,07</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-77,74; 17,41</t>
+          <t>-76,2; 20,04</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-62,53; 41,3</t>
+          <t>-64,24; 38,41</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-66,65; -6,17</t>
+          <t>-66,01; -0,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-65,26; -2,69</t>
+          <t>-68,92; -2,75</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-63,2; -13,71</t>
+          <t>-63,63; -10,2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-56,85; -0,71</t>
+          <t>-54,68; 0,76</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 0,49</t>
+          <t>-5,82; 0,78</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6,24; 14,0</t>
+          <t>6,17; 14,33</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 4,95</t>
+          <t>-3,72; 5,11</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14,01; 24,01</t>
+          <t>13,98; 23,48</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,56</t>
+          <t>-3,56; 1,67</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,97; 17,51</t>
+          <t>10,95; 17,58</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-79,92; 28,42</t>
+          <t>-81,69; 30,21</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>79,52; 456,38</t>
+          <t>81,7; 504,15</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-47,02; 111,12</t>
+          <t>-45,78; 130,45</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>148,39; 561,7</t>
+          <t>147,4; 582,25</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-54,09; 39,86</t>
+          <t>-52,85; 38,51</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>143,66; 412,07</t>
+          <t>144,69; 432,39</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,56</t>
+          <t>-0,39; 3,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,32; 8,14</t>
+          <t>3,29; 8,28</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 3,22</t>
+          <t>-3,08; 3,32</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 12,67</t>
+          <t>-2,37; 12,99</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,64</t>
+          <t>-1,2; 2,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,93; 9,58</t>
+          <t>1,83; 9,78</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 199,94</t>
+          <t>-15,04; 193,35</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>82,92; 481,93</t>
+          <t>81,66; 448,16</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-30,0; 44,69</t>
+          <t>-29,98; 43,95</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-18,96; 148,01</t>
+          <t>-19,29; 156,61</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 54,72</t>
+          <t>-17,46; 54,14</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>30,08; 183,11</t>
+          <t>32,48; 184,75</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,06</t>
+          <t>0,02; 3,01</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,39</t>
+          <t>-0,56; 3,42</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 5,43</t>
+          <t>-0,0; 5,79</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,49; 8,37</t>
+          <t>2,51; 8,22</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,86</t>
+          <t>0,42; 3,85</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 4,54</t>
+          <t>-0,24; 4,79</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 307,24</t>
+          <t>-4,52; 284,79</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-26,55; 285,58</t>
+          <t>-22,12; 279,89</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 85,77</t>
+          <t>-1,18; 95,42</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>27,25; 145,18</t>
+          <t>29,17; 133,13</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,18; 99,64</t>
+          <t>7,64; 100,34</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 111,29</t>
+          <t>-3,43; 121,26</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,46</t>
+          <t>-1,27; 0,53</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,26</t>
+          <t>1,58; 4,26</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,14</t>
+          <t>-1,62; 1,25</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,33</t>
+          <t>1,94; 6,27</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,54</t>
+          <t>-1,19; 0,46</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,01</t>
+          <t>2,5; 5,06</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-31,8; 15,34</t>
+          <t>-31,62; 18,63</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>36,77; 134,22</t>
+          <t>43,31; 140,62</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 13,27</t>
+          <t>-16,7; 14,98</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>17,52; 72,53</t>
+          <t>22,68; 72,69</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 8,71</t>
+          <t>-17,1; 7,62</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>37,56; 82,08</t>
+          <t>37,83; 83,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_Lim_5-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_5-Provincia-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-1,4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,56</t>
+          <t>-2,51</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,04</t>
+          <t>-1,93</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 3,25</t>
+          <t>-3,49; 2,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 1,16</t>
+          <t>-4,34; 1,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 11,07</t>
+          <t>-0,78; 10,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 1,12</t>
+          <t>-6,82; 0,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 5,44</t>
+          <t>-0,86; 5,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 0,27</t>
+          <t>-4,84; 0,33</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-37,35%</t>
+          <t>-36,07%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-30,69%</t>
+          <t>-30,01%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-33,49%</t>
+          <t>-31,74%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-63,86; 152,74</t>
+          <t>-61,87; 130,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-73,8; 54,94</t>
+          <t>-75,1; 56,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 182,48</t>
+          <t>-9,03; 169,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-61,11; 20,85</t>
+          <t>-58,42; 19,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,58; 116,41</t>
+          <t>-13,22; 112,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,64; 6,19</t>
+          <t>-58,66; 7,59</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,17</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,08</t>
+          <t>2,15</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,0; -2,01</t>
+          <t>-6,72; -2,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 2,86</t>
+          <t>-2,6; 3,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; -0,26</t>
+          <t>-7,0; -0,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,75</t>
+          <t>0,24; 7,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,94; -1,81</t>
+          <t>-5,74; -1,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,3</t>
+          <t>-0,11; 4,64</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-93,77; -50,59</t>
+          <t>-95,04; -51,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,37; 87,5</t>
+          <t>-40,17; 105,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,73; -0,33</t>
+          <t>-64,04; -3,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 111,55</t>
+          <t>2,64; 107,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,05; -29,73</t>
+          <t>-71,57; -31,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 73,4</t>
+          <t>-1,09; 86,15</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8,12</t>
+          <t>8,01</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,89</t>
+          <t>7,75</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,06</t>
+          <t>7,96</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,91</t>
+          <t>-4,1; 0,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 11,51</t>
+          <t>4,5; 11,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 1,31</t>
+          <t>-7,34; 1,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,38; 12,28</t>
+          <t>3,34; 11,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 0,16</t>
+          <t>-4,53; 0,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,01; 10,85</t>
+          <t>5,32; 10,87</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>288,86%</t>
+          <t>284,94%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>145,7%</t>
+          <t>143,9%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-85,64; 82,41</t>
+          <t>-86,82; 65,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73,57; 853,22</t>
+          <t>73,13; 813,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-65,85; 28,86</t>
+          <t>-68,32; 32,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,75; 220,74</t>
+          <t>29,65; 190,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,32; 4,8</t>
+          <t>-65,17; 6,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,57; 255,73</t>
+          <t>72,22; 269,54</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5,46</t>
+          <t>4,57</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,31</t>
+          <t>3,02</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 3,85</t>
+          <t>-2,34; 3,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 9,38</t>
+          <t>1,17; 8,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 4,32</t>
+          <t>-5,83; 4,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 3,75</t>
+          <t>-3,46; 5,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 2,54</t>
+          <t>-2,83; 2,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 5,34</t>
+          <t>0,2; 5,79</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>132,84%</t>
+          <t>111,29%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-9,03%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,86; 140,98</t>
+          <t>-40,78; 125,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,32; 362,13</t>
+          <t>12,03; 303,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 39,23</t>
+          <t>-37,75; 39,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-47,0; 31,95</t>
+          <t>-21,28; 48,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,24; 34,17</t>
+          <t>-27,75; 39,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 70,1</t>
+          <t>1,13; 76,3</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-2,45</t>
+          <t>-2,98</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-5,98</t>
+          <t>-4,26</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,77</t>
+          <t>-3,48</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 1,0</t>
+          <t>-8,74; 0,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 1,9</t>
+          <t>-7,95; 1,54</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,98; -0,47</t>
+          <t>-14,42; -0,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,33; -0,17</t>
+          <t>-11,11; 1,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,15; -1,21</t>
+          <t>-10,49; -1,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 0,07</t>
+          <t>-7,29; 0,61</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-29,62%</t>
+          <t>-36,01%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-34,29%</t>
+          <t>-24,43%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-29,18%</t>
+          <t>-26,94%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-76,2; 20,04</t>
+          <t>-75,01; 23,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-64,24; 38,41</t>
+          <t>-70,1; 30,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-66,01; -0,57</t>
+          <t>-66,85; -4,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-68,92; -2,75</t>
+          <t>-48,48; 13,96</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-63,63; -10,2</t>
+          <t>-65,0; -15,66</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-54,68; 0,76</t>
+          <t>-46,57; 6,62</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10,04</t>
+          <t>10,03</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18,91</t>
+          <t>19,04</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,35</t>
+          <t>14,46</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,78</t>
+          <t>-5,77; 0,79</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6,17; 14,33</t>
+          <t>6,01; 14,77</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 5,11</t>
+          <t>-3,51; 4,97</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13,98; 23,48</t>
+          <t>13,93; 23,93</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 1,67</t>
+          <t>-3,59; 1,52</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,95; 17,58</t>
+          <t>11,33; 17,64</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>204,3%</t>
+          <t>204,18%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>301,08%</t>
+          <t>303,06%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>255,94%</t>
+          <t>257,97%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-81,69; 30,21</t>
+          <t>-82,53; 34,99</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>81,7; 504,15</t>
+          <t>70,46; 497,97</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-45,78; 130,45</t>
+          <t>-46,32; 120,84</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>147,4; 582,25</t>
+          <t>157,88; 576,83</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-52,85; 38,51</t>
+          <t>-52,18; 36,74</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>144,69; 432,39</t>
+          <t>153,19; 434,83</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>5,64</t>
+          <t>5,53</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6,88</t>
+          <t>11,72</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,78</t>
+          <t>8,78</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,41</t>
+          <t>-0,5; 3,59</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3,29; 8,28</t>
+          <t>3,25; 8,01</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 3,32</t>
+          <t>-3,37; 2,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 12,99</t>
+          <t>7,98; 15,07</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,63</t>
+          <t>-1,14; 2,72</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,83; 9,78</t>
+          <t>6,44; 10,81</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>217,81%</t>
+          <t>213,69%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>128,97%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>114,59%</t>
+          <t>148,4%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 193,35</t>
+          <t>-14,22; 214,94</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>81,66; 448,16</t>
+          <t>85,14; 475,52</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 43,95</t>
+          <t>-31,72; 38,76</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 156,61</t>
+          <t>72,03; 207,89</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 54,14</t>
+          <t>-17,32; 54,93</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>32,48; 184,75</t>
+          <t>89,46; 221,04</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5,11</t>
+          <t>4,29</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>3,46</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,02; 3,01</t>
+          <t>0,01; 3,2</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,42</t>
+          <t>1,14; 4,3</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 5,79</t>
+          <t>0,11; 5,58</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,22</t>
+          <t>1,58; 6,89</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,85</t>
+          <t>0,3; 3,71</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 4,79</t>
+          <t>1,92; 4,94</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>158,53%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 284,79</t>
+          <t>-6,9; 303,49</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 279,89</t>
+          <t>35,44; 412,3</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 95,42</t>
+          <t>1,47; 93,66</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>29,17; 133,13</t>
+          <t>17,61; 115,73</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,64; 100,34</t>
+          <t>5,41; 92,76</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 121,26</t>
+          <t>34,59; 129,18</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3,09</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>5,76</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>4,64</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,53</t>
+          <t>-1,4; 0,49</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,26</t>
+          <t>2,48; 4,49</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 1,25</t>
+          <t>-1,81; 1,27</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,27</t>
+          <t>4,38; 7,17</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,46</t>
+          <t>-1,24; 0,46</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,06</t>
+          <t>3,79; 5,59</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 18,63</t>
+          <t>-34,02; 16,63</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>43,31; 140,62</t>
+          <t>59,07; 148,09</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-16,7; 14,98</t>
+          <t>-17,81; 14,7</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>22,68; 72,69</t>
+          <t>42,01; 84,3</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-17,1; 7,62</t>
+          <t>-17,89; 7,54</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>37,83; 83,86</t>
+          <t>54,68; 92,21</t>
         </is>
       </c>
     </row>
